--- a/408自主选课打卡清单_已修复.xlsx
+++ b/408自主选课打卡清单_已修复.xlsx
@@ -939,7 +939,7 @@
       </c>
       <c r="C15" s="13" t="n"/>
       <c r="D15" s="14">
-        <f>SUMIF($A$5:$A$14,1,$D$5:$D$14)</f>
+        <f>SUMIF($C$5:$C$14,"&lt;&gt;",$D$5:$D$14)</f>
         <v/>
       </c>
       <c r="E15" s="10" t="n"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C27" s="13" t="n"/>
       <c r="D27" s="14">
-        <f>SUMIF($A$17:$A$26,1,$D$17:$D$26)</f>
+        <f>SUMIF($C$17:$C$26,"&lt;&gt;",$D$17:$D$26)</f>
         <v/>
       </c>
       <c r="E27" s="10" t="n"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C39" s="13" t="n"/>
       <c r="D39" s="14">
-        <f>SUMIF($A$29:$A$38,1,$D$29:$D$38)</f>
+        <f>SUMIF($C$29:$C$38,"&lt;&gt;",$D$29:$D$38)</f>
         <v/>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C51" s="13" t="n"/>
       <c r="D51" s="14">
-        <f>SUMIF($A$41:$A$50,1,$D$41:$D$50)</f>
+        <f>SUMIF($C$41:$C$50,"&lt;&gt;",$D$41:$D$50)</f>
         <v/>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C63" s="13" t="n"/>
       <c r="D63" s="14">
-        <f>SUMIF($A$53:$A$62,1,$D$53:$D$62)</f>
+        <f>SUMIF($C$53:$C$62,"&lt;&gt;",$D$53:$D$62)</f>
         <v/>
       </c>
       <c r="E63" s="10" t="n"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C75" s="13" t="n"/>
       <c r="D75" s="14">
-        <f>SUMIF($A$65:$A$74,1,$D$65:$D$74)</f>
+        <f>SUMIF($C$65:$C$74,"&lt;&gt;",$D$65:$D$74)</f>
         <v/>
       </c>
       <c r="E75" s="10" t="n"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C87" s="13" t="n"/>
       <c r="D87" s="14">
-        <f>SUMIF($A$77:$A$86,1,$D$77:$D$86)</f>
+        <f>SUMIF($C$77:$C$86,"&lt;&gt;",$D$77:$D$86)</f>
         <v/>
       </c>
       <c r="E87" s="10" t="n"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C99" s="13" t="n"/>
       <c r="D99" s="14">
-        <f>SUMIF($A$89:$A$98,1,$D$89:$D$98)</f>
+        <f>SUMIF($C$89:$C$98,"&lt;&gt;",$D$89:$D$98)</f>
         <v/>
       </c>
       <c r="E99" s="10" t="n"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C111" s="13" t="n"/>
       <c r="D111" s="14">
-        <f>SUMIF($A$101:$A$110,1,$D$101:$D$110)</f>
+        <f>SUMIF($C$101:$C$110,"&lt;&gt;",$D$101:$D$110)</f>
         <v/>
       </c>
       <c r="E111" s="10" t="n"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C123" s="13" t="n"/>
       <c r="D123" s="14">
-        <f>SUMIF($A$113:$A$122,1,$D$113:$D$122)</f>
+        <f>SUMIF($C$113:$C$122,"&lt;&gt;",$D$113:$D$122)</f>
         <v/>
       </c>
       <c r="E123" s="10" t="n"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C135" s="13" t="n"/>
       <c r="D135" s="14">
-        <f>SUMIF($A$125:$A$134,1,$D$125:$D$134)</f>
+        <f>SUMIF($C$125:$C$134,"&lt;&gt;",$D$125:$D$134)</f>
         <v/>
       </c>
       <c r="E135" s="10" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="C147" s="13" t="n"/>
       <c r="D147" s="14">
-        <f>SUMIF($A$137:$A$146,1,$D$137:$D$146)</f>
+        <f>SUMIF($C$137:$C$146,"&lt;&gt;",$D$137:$D$146)</f>
         <v/>
       </c>
       <c r="E147" s="10" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C159" s="13" t="n"/>
       <c r="D159" s="14">
-        <f>SUMIF($A$149:$A$158,1,$D$149:$D$158)</f>
+        <f>SUMIF($C$149:$C$158,"&lt;&gt;",$D$149:$D$158)</f>
         <v/>
       </c>
       <c r="E159" s="10" t="n"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C171" s="13" t="n"/>
       <c r="D171" s="14">
-        <f>SUMIF($A$161:$A$170,1,$D$161:$D$170)</f>
+        <f>SUMIF($C$161:$C$170,"&lt;&gt;",$D$161:$D$170)</f>
         <v/>
       </c>
       <c r="E171" s="10" t="n"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C183" s="13" t="n"/>
       <c r="D183" s="14">
-        <f>SUMIF($A$173:$A$182,1,$D$173:$D$182)</f>
+        <f>SUMIF($C$173:$C$182,"&lt;&gt;",$D$173:$D$182)</f>
         <v/>
       </c>
       <c r="E183" s="10" t="n"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C195" s="13" t="n"/>
       <c r="D195" s="14">
-        <f>SUMIF($A$185:$A$194,1,$D$185:$D$194)</f>
+        <f>SUMIF($C$185:$C$194,"&lt;&gt;",$D$185:$D$194)</f>
         <v/>
       </c>
       <c r="E195" s="10" t="n"/>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C207" s="13" t="n"/>
       <c r="D207" s="14">
-        <f>SUMIF($A$197:$A$206,1,$D$197:$D$206)</f>
+        <f>SUMIF($C$197:$C$206,"&lt;&gt;",$D$197:$D$206)</f>
         <v/>
       </c>
       <c r="E207" s="10" t="n"/>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C219" s="13" t="n"/>
       <c r="D219" s="14">
-        <f>SUMIF($A$209:$A$218,1,$D$209:$D$218)</f>
+        <f>SUMIF($C$209:$C$218,"&lt;&gt;",$D$209:$D$218)</f>
         <v/>
       </c>
       <c r="E219" s="10" t="n"/>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C231" s="13" t="n"/>
       <c r="D231" s="14">
-        <f>SUMIF($A$221:$A$230,1,$D$221:$D$230)</f>
+        <f>SUMIF($C$221:$C$230,"&lt;&gt;",$D$221:$D$230)</f>
         <v/>
       </c>
       <c r="E231" s="10" t="n"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C243" s="13" t="n"/>
       <c r="D243" s="14">
-        <f>SUMIF($A$233:$A$242,1,$D$233:$D$242)</f>
+        <f>SUMIF($C$233:$C$242,"&lt;&gt;",$D$233:$D$242)</f>
         <v/>
       </c>
       <c r="E243" s="10" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C255" s="13" t="n"/>
       <c r="D255" s="14">
-        <f>SUMIF($A$245:$A$254,1,$D$245:$D$254)</f>
+        <f>SUMIF($C$245:$C$254,"&lt;&gt;",$D$245:$D$254)</f>
         <v/>
       </c>
       <c r="E255" s="10" t="n"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C267" s="13" t="n"/>
       <c r="D267" s="14">
-        <f>SUMIF($A$257:$A$266,1,$D$257:$D$266)</f>
+        <f>SUMIF($C$257:$C$266,"&lt;&gt;",$D$257:$D$266)</f>
         <v/>
       </c>
       <c r="E267" s="10" t="n"/>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C279" s="13" t="n"/>
       <c r="D279" s="14">
-        <f>SUMIF($A$269:$A$278,1,$D$269:$D$278)</f>
+        <f>SUMIF($C$269:$C$278,"&lt;&gt;",$D$269:$D$278)</f>
         <v/>
       </c>
       <c r="E279" s="10" t="n"/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C291" s="13" t="n"/>
       <c r="D291" s="14">
-        <f>SUMIF($A$281:$A$290,1,$D$281:$D$290)</f>
+        <f>SUMIF($C$281:$C$290,"&lt;&gt;",$D$281:$D$290)</f>
         <v/>
       </c>
       <c r="E291" s="10" t="n"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C303" s="13" t="n"/>
       <c r="D303" s="14">
-        <f>SUMIF($A$293:$A$302,1,$D$293:$D$302)</f>
+        <f>SUMIF($C$293:$C$302,"&lt;&gt;",$D$293:$D$302)</f>
         <v/>
       </c>
       <c r="E303" s="10" t="n"/>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C315" s="13" t="n"/>
       <c r="D315" s="14">
-        <f>SUMIF($A$305:$A$314,1,$D$305:$D$314)</f>
+        <f>SUMIF($C$305:$C$314,"&lt;&gt;",$D$305:$D$314)</f>
         <v/>
       </c>
       <c r="E315" s="10" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C327" s="13" t="n"/>
       <c r="D327" s="14">
-        <f>SUMIF($A$317:$A$326,1,$D$317:$D$326)</f>
+        <f>SUMIF($C$317:$C$326,"&lt;&gt;",$D$317:$D$326)</f>
         <v/>
       </c>
       <c r="E327" s="10" t="n"/>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C339" s="13" t="n"/>
       <c r="D339" s="14">
-        <f>SUMIF($A$329:$A$338,1,$D$329:$D$338)</f>
+        <f>SUMIF($C$329:$C$338,"&lt;&gt;",$D$329:$D$338)</f>
         <v/>
       </c>
       <c r="E339" s="10" t="n"/>

--- a/408自主选课打卡清单_已修复.xlsx
+++ b/408自主选课打卡清单_已修复.xlsx
@@ -187,6 +187,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -4678,12 +4688,20 @@
     <mergeCell ref="B315:C315"/>
     <mergeCell ref="B75:C75"/>
   </mergeCells>
-  <dataValidations count="2">
+  <conditionalFormatting sqref="A5:F14 A17:F26 A29:F38 A41:F50 A53:F62 A65:F74 A77:F86 A89:F98 A101:F110 A113:F122 A125:F134 A137:F146 A149:F158 A161:F170 A173:F182 A185:F194 A197:F206 A209:F218 A221:F230 A233:F242 A245:F254 A257:F266 A269:F278 A281:F290 A293:F302 A305:F314 A317:F326 A329:F338">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>=$A5="☑"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
     <dataValidation sqref="B5:B340" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"组成原理强化,操作系统强化,计网强化,数据结构强化,真题分类"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C340" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=INDIRECT($B5)</formula1>
+    </dataValidation>
+    <dataValidation sqref="A5:A14 A17:A26 A29:A38 A41:A50 A53:A62 A65:A74 A77:A86 A89:A98 A101:A110 A113:A122 A125:A134 A137:A146 A149:A158 A161:A170 A173:A182 A185:A194 A197:A206 A209:A218 A221:A230 A233:A242 A245:A254 A257:A266 A269:A278 A281:A290 A293:A302 A305:A314 A317:A326 A329:A338" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
